--- a/data/filtered/china_noir.xlsx
+++ b/data/filtered/china_noir.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,6 +459,31 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>是否春节档</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>是否国庆档</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>是否五一档</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>是否暑期档</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>是否普通周末</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>详情链接</t>
         </is>
       </c>
@@ -498,7 +523,22 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35914241/</t>
         </is>
@@ -539,7 +579,22 @@
           <t>2006</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1870452/</t>
         </is>
@@ -580,7 +635,22 @@
           <t>2005</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2244756/</t>
         </is>
@@ -621,7 +691,22 @@
           <t>2005</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2357298/</t>
         </is>
@@ -662,7 +747,22 @@
           <t>2018-02-24</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30145577/</t>
         </is>
@@ -703,7 +803,22 @@
           <t>2015-03-25</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/10743802/</t>
         </is>
